--- a/Mod_Korean/Lang/KR/Dialog/Drama/_adv.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/_adv.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="god" sheetId="1" r:id="rId3"/>
-    <sheet name="general" sheetId="2" r:id="rId4"/>
+    <sheet name="god" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="general" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="139">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -152,6 +152,12 @@
 #god_benefit</t>
   </si>
   <si>
+    <t xml:space="preserve">당신은 제단에 다가가면서, 신들에 얽힌 여러 전승을 떠올렸다.
+■신앙 《#god_name》
+#god_desc
+#god_benefit</t>
+  </si>
+  <si>
     <t xml:space="preserve">worship2</t>
   </si>
   <si>
@@ -164,6 +170,9 @@
     <t xml:space="preserve">Worship #god_name.</t>
   </si>
   <si>
+    <t xml:space="preserve">#god_name을(를) 믿는다</t>
+  </si>
+  <si>
     <t xml:space="preserve">end</t>
   </si>
   <si>
@@ -171,6 +180,9 @@
   </si>
   <si>
     <t xml:space="preserve">(Leave)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">떠난다</t>
   </si>
   <si>
     <t xml:space="preserve">cancel</t>
@@ -187,6 +199,10 @@
 "#godtalk_worship"</t>
   </si>
   <si>
+    <t xml:space="preserve">당신의 머릿속에 신비한 목소리가 울렸다.
+「#godtalk_worship」</t>
+  </si>
+  <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
@@ -194,6 +210,9 @@
   </si>
   <si>
     <t xml:space="preserve">Marriage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결혼</t>
   </si>
   <si>
     <t xml:space="preserve">marry</t>
@@ -216,6 +235,10 @@
 The two stood in silence, hands entwined, and pledged their love to last forever.</t>
   </si>
   <si>
+    <t xml:space="preserve">시에라력 #1년 #2, #3에서, #4은(는) #5에게 프로포즈했다.
+두 사람은 조용히 손을 맞잡고, 영원한 사랑을 이곳에서 맹세했다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">marry2</t>
   </si>
   <si>
@@ -223,6 +246,9 @@
   </si>
   <si>
     <t xml:space="preserve">Without you, life has no meaning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">평생을 당신에게 바친다</t>
   </si>
   <si>
     <t xml:space="preserve">invoke</t>
@@ -268,6 +294,11 @@
 When the moonlight spills down upon the earth, under an eternal vow, the two shall be firmly bound as one.</t>
   </si>
   <si>
+    <t xml:space="preserve">잠들지 않는 별들이여, 돌고 도는 달이여. 오늘 밤, 이 두 사람의 새로운 출발을 지켜보며 이 행운의 날을 축복하소서.
+밤하늘에 바쳐진 꽃다발이, 내일로 이어지는 입맞춤이, 머지않아 황금빛으로 빛나는 시간을 맺게 하리라.
+달빛이 지상으로 넘쳐흐르는 그 때, 영원한 맹세 아래 두 사람은 굳게 맺어지리라.</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.5,1</t>
   </si>
   <si>
@@ -279,6 +310,10 @@
 Do you swear to take #tg as your lifelong partner, to never let go of #tg_his hand in joyful mornings or tearful nights, and to remain by #tg_his side forever?</t>
   </si>
   <si>
+    <t xml:space="preserve">#pc_full.
+그대는 #tg을(를) 평생의 반려로 맞아, 기쁨의 아침에도, 눈물의 밤에도, 그 손을 놓지 않고 영원히 그 곁을 지킬 것을 맹세하는가?</t>
+  </si>
+  <si>
     <t xml:space="preserve">wedding2</t>
   </si>
   <si>
@@ -288,6 +323,9 @@
     <t xml:space="preserve">Yes.</t>
   </si>
   <si>
+    <t xml:space="preserve">네</t>
+  </si>
+  <si>
     <t xml:space="preserve">wedding_fail</t>
   </si>
   <si>
@@ -295,6 +333,9 @@
   </si>
   <si>
     <t xml:space="preserve">No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아니요</t>
   </si>
   <si>
     <t xml:space="preserve">…</t>
@@ -311,10 +352,17 @@
 Do you swear to take #pc_full as your one and only partner, to entrust your heart through storms of fate and in peaceful slumber, and to walk together always?</t>
   </si>
   <si>
+    <t xml:space="preserve">#tg.
+그대는 #pc_full을(를) 유일한 반려로 맞아, 운명의 폭풍 속에서도, 고요한 잠에 들면서도, 그 마음을 맡기고 함께 걸어나갈 것을 맹세하는가?</t>
+  </si>
+  <si>
     <t xml:space="preserve">…はい。</t>
   </si>
   <si>
     <t xml:space="preserve">...Yes, I do.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…네.</t>
   </si>
   <si>
     <t xml:space="preserve">星々の証人のもと、これにて二人はひとつに結ばれた。汝らに幸運の女神の祝福あれ…！ 
@@ -323,6 +371,29 @@
   <si>
     <t xml:space="preserve">Before the witness of the stars, these two are now united as one. May the goddess of fortune bless you both!
 Now... the kiss of your vow.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">별들의 증언 아래, 이로써 두 사람은 하나로 맺어졌다. 그대들에게 행운의 여신의 축복 있으라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…!
+이제… 맹세의 입맞춤을.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">wedding3</t>
@@ -334,6 +405,9 @@
     <t xml:space="preserve">(Kiss #tg_him)</t>
   </si>
   <si>
+    <t xml:space="preserve">맹세의 입맞춤을 한다</t>
+  </si>
+  <si>
     <t xml:space="preserve">wedding5</t>
   </si>
   <si>
@@ -341,6 +415,9 @@
   </si>
   <si>
     <t xml:space="preserve">(Make love with #tg_him)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기분 좋은 일을 한다</t>
   </si>
   <si>
     <t xml:space="preserve">wedding4</t>
@@ -352,10 +429,16 @@
     <t xml:space="preserve">(Blush and stay silent)</t>
   </si>
   <si>
+    <t xml:space="preserve">부끄러워서 입을 다문다</t>
+  </si>
+  <si>
     <t xml:space="preserve">逃げる</t>
   </si>
   <si>
     <t xml:space="preserve">(Run away)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도망간다</t>
   </si>
   <si>
     <r>
@@ -391,6 +474,9 @@
   </si>
   <si>
     <t xml:space="preserve">(#tg smiles shyly and quietly presses #tg_his lip to yours.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg은(는) 부끄러운 듯 미소짓고 당신과 조용히 입을 맞추었다)</t>
   </si>
   <si>
     <t xml:space="preserve">wedding_fin</t>
@@ -431,6 +517,9 @@
     <t xml:space="preserve">(#tg lets out a soft laugh and gently brings #tg_his lip to yours.) </t>
   </si>
   <si>
+    <t xml:space="preserve">(#tg은(는) 가볍게 웃음짓고는 당신과 살며시 입을 맞추었다)</t>
+  </si>
+  <si>
     <t xml:space="preserve">clap3</t>
   </si>
   <si>
@@ -455,23 +544,7 @@
     <t xml:space="preserve">What?</t>
   </si>
   <si>
-    <t xml:space="preserve">당신은 제단에 다가가면서, 신들에 얽힌 여러 전승을 떠올렸다.
-■신앙 《#god_name》
-#god_desc
-#god_benefit</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">#god_name을(를) 믿는다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">떠난다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">당신의 머릿속에 신비한 목소리가 울렸다.
-「#godtalk_worship」</t>
+    <t xml:space="preserve">…에?</t>
   </si>
 </sst>
 </file>
@@ -482,7 +555,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -493,26 +566,33 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
-      <charset val="128"/>
+      <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
-      <charset val="128"/>
+      <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
-      <charset val="128"/>
+      <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -537,7 +617,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -546,62 +626,86 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -615,13 +719,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -698,37 +802,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -797,24 +901,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW442"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="29.34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,13 +954,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -863,7 +968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
@@ -871,7 +976,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -879,7 +984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
@@ -887,7 +992,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
@@ -895,7 +1000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -903,7 +1008,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
@@ -911,7 +1016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
@@ -919,7 +1024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
@@ -927,7 +1032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
@@ -935,7 +1040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
@@ -943,7 +1048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
@@ -951,7 +1056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -959,7 +1064,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
         <v>13</v>
       </c>
@@ -967,7 +1072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
@@ -975,7 +1080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>13</v>
       </c>
@@ -983,7 +1088,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>13</v>
       </c>
@@ -991,7 +1096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
@@ -999,7 +1104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1007,7 +1112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1015,17 +1120,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1033,7 +1138,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="12.8">
+    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1296,11 +1401,11 @@
       <c r="IV29" s="1"/>
       <c r="IW29" s="1"/>
     </row>
-    <row r="30" ht="74.6">
+    <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -1310,7 +1415,7 @@
         <v>40</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1559,98 +1664,98 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K31" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K31" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
-      <c r="B32" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="H32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
-      <c r="K32" t="s">
-        <v>121</v>
+      <c r="K32" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" ht="32.8">
+    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
-      <c r="K37" t="s">
-        <v>122</v>
+      <c r="K37" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -1899,7 +2004,7 @@
       <c r="IV40" s="1"/>
       <c r="IW40" s="1"/>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="1"/>
@@ -2150,23 +2255,23 @@
       <c r="IV44" s="1"/>
       <c r="IW44" s="1"/>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="64" s="3" customFormat="1" ht="12.8">
+    <row r="64" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2425,7 +2530,7 @@
       <c r="IV64" s="1"/>
       <c r="IW64" s="1"/>
     </row>
-    <row r="66" ht="12.8">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -2674,7 +2779,7 @@
       <c r="IV66" s="1"/>
       <c r="IW66" s="1"/>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -2923,7 +3028,7 @@
       <c r="IV67" s="1"/>
       <c r="IW67" s="1"/>
     </row>
-    <row r="68" s="5" customFormat="1" ht="12.8">
+    <row r="68" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3182,7 +3287,7 @@
       <c r="IV68" s="1"/>
       <c r="IW68" s="1"/>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -3431,7 +3536,7 @@
       <c r="IV70" s="1"/>
       <c r="IW70" s="1"/>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3680,7 +3785,7 @@
       <c r="IV71" s="1"/>
       <c r="IW71" s="1"/>
     </row>
-    <row r="85" s="3" customFormat="1" ht="12.8">
+    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3939,7 +4044,7 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -4188,7 +4293,7 @@
       <c r="IV87" s="1"/>
       <c r="IW87" s="1"/>
     </row>
-    <row r="88" ht="12.8">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -4437,7 +4542,7 @@
       <c r="IV88" s="1"/>
       <c r="IW88" s="1"/>
     </row>
-    <row r="89" s="5" customFormat="1" ht="12.8">
+    <row r="89" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4696,7 +4801,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="91" ht="12.8">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
@@ -4945,7 +5050,7 @@
       <c r="IV91" s="1"/>
       <c r="IW91" s="1"/>
     </row>
-    <row r="92" ht="12.8">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
@@ -5194,7 +5299,7 @@
       <c r="IV92" s="1"/>
       <c r="IW92" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="1" ht="12.8">
+    <row r="99" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5453,7 +5558,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="101" ht="12.8">
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
@@ -5702,7 +5807,7 @@
       <c r="IV101" s="1"/>
       <c r="IW101" s="1"/>
     </row>
-    <row r="102" ht="12.8">
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
@@ -5951,7 +6056,7 @@
       <c r="IV102" s="1"/>
       <c r="IW102" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="1" ht="12.8">
+    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -6210,7 +6315,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="1" ht="12.8">
+    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -6469,7 +6574,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="1" ht="12.8">
+    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -6728,7 +6833,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="120" ht="12.8">
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -6977,7 +7082,7 @@
       <c r="IV120" s="1"/>
       <c r="IW120" s="1"/>
     </row>
-    <row r="121" ht="12.8">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
@@ -7226,7 +7331,7 @@
       <c r="IV121" s="1"/>
       <c r="IW121" s="1"/>
     </row>
-    <row r="122" ht="12.8">
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
@@ -7475,7 +7580,7 @@
       <c r="IV122" s="1"/>
       <c r="IW122" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="1" ht="12.8">
+    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7734,7 +7839,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="1" ht="12.8">
+    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7993,7 +8098,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="1" ht="12.8">
+    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -8252,7 +8357,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="1" ht="12.8">
+    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8511,7 +8616,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="1" ht="12.8">
+    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8770,7 +8875,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="131" ht="12.8">
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
@@ -9019,7 +9124,7 @@
       <c r="IV131" s="1"/>
       <c r="IW131" s="1"/>
     </row>
-    <row r="132" ht="12.8">
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
@@ -9268,7 +9373,7 @@
       <c r="IV132" s="1"/>
       <c r="IW132" s="1"/>
     </row>
-    <row r="133" ht="12.8">
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
@@ -9517,7 +9622,7 @@
       <c r="IV133" s="1"/>
       <c r="IW133" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="1" ht="12.8">
+    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -9776,7 +9881,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="159" ht="12.8">
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
@@ -10025,7 +10130,7 @@
       <c r="IV159" s="1"/>
       <c r="IW159" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="1" ht="12.8">
+    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -10284,7 +10389,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="1" ht="12.8">
+    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -10543,7 +10648,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="162" ht="12.8">
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
@@ -10792,7 +10897,7 @@
       <c r="IV162" s="1"/>
       <c r="IW162" s="1"/>
     </row>
-    <row r="163" ht="12.8">
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
@@ -11041,7 +11146,7 @@
       <c r="IV163" s="1"/>
       <c r="IW163" s="1"/>
     </row>
-    <row r="164" ht="12.8">
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K164" s="1"/>
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
@@ -11290,7 +11395,7 @@
       <c r="IV164" s="1"/>
       <c r="IW164" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="1" ht="12.8">
+    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -11549,7 +11654,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="238" ht="12.8">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
@@ -11798,7 +11903,7 @@
       <c r="IV238" s="1"/>
       <c r="IW238" s="1"/>
     </row>
-    <row r="239" ht="12.8">
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
@@ -12047,7 +12152,7 @@
       <c r="IV239" s="1"/>
       <c r="IW239" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="1" ht="12.8">
+    <row r="240" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -12306,7 +12411,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="242" ht="12.8">
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
@@ -12555,7 +12660,7 @@
       <c r="IV242" s="1"/>
       <c r="IW242" s="1"/>
     </row>
-    <row r="243" ht="12.8">
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
@@ -12804,7 +12909,7 @@
       <c r="IV243" s="1"/>
       <c r="IW243" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="1" ht="12.8">
+    <row r="272" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -13063,7 +13168,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="274" ht="12.8">
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
@@ -13312,7 +13417,7 @@
       <c r="IV274" s="1"/>
       <c r="IW274" s="1"/>
     </row>
-    <row r="275" ht="12.8">
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
@@ -13561,7 +13666,7 @@
       <c r="IV275" s="1"/>
       <c r="IW275" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="1" ht="12.8">
+    <row r="286" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -13820,7 +13925,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="1" ht="12.8">
+    <row r="287" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -14079,7 +14184,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="288" ht="12.8">
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
@@ -14328,7 +14433,7 @@
       <c r="IV288" s="1"/>
       <c r="IW288" s="1"/>
     </row>
-    <row r="289" ht="12.8">
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K289" s="1"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
@@ -14577,7 +14682,7 @@
       <c r="IV289" s="1"/>
       <c r="IW289" s="1"/>
     </row>
-    <row r="290" ht="12.8">
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
@@ -14826,7 +14931,7 @@
       <c r="IV290" s="1"/>
       <c r="IW290" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="1" ht="12.8">
+    <row r="300" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -15085,7 +15190,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="302" ht="12.8">
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
@@ -15334,7 +15439,7 @@
       <c r="IV302" s="1"/>
       <c r="IW302" s="1"/>
     </row>
-    <row r="303" ht="12.8">
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
@@ -15583,7 +15688,7 @@
       <c r="IV303" s="1"/>
       <c r="IW303" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="1" ht="12.8">
+    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -15842,7 +15947,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="308" ht="12.8">
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
@@ -16091,7 +16196,7 @@
       <c r="IV308" s="1"/>
       <c r="IW308" s="1"/>
     </row>
-    <row r="309" ht="12.8">
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
@@ -16340,7 +16445,7 @@
       <c r="IV309" s="1"/>
       <c r="IW309" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="1" ht="12.8">
+    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -16599,7 +16704,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="315" ht="12.8">
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
@@ -16848,7 +16953,7 @@
       <c r="IV315" s="1"/>
       <c r="IW315" s="1"/>
     </row>
-    <row r="316" ht="12.8">
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
@@ -17097,7 +17202,7 @@
       <c r="IV316" s="1"/>
       <c r="IW316" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="1" ht="12.8">
+    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -17356,7 +17461,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="339" ht="12.8">
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
@@ -17605,7 +17710,7 @@
       <c r="IV339" s="1"/>
       <c r="IW339" s="1"/>
     </row>
-    <row r="340" ht="12.8">
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
@@ -17854,7 +17959,7 @@
       <c r="IV340" s="1"/>
       <c r="IW340" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="1" ht="12.8">
+    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -18113,7 +18218,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="350" ht="12.8">
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K350" s="1"/>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
@@ -18362,7 +18467,7 @@
       <c r="IV350" s="1"/>
       <c r="IW350" s="1"/>
     </row>
-    <row r="351" ht="12.8">
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K351" s="1"/>
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
@@ -18611,7 +18716,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="1" ht="12.8">
+    <row r="354" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -18870,7 +18975,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="1" ht="12.8">
+    <row r="355" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -19129,7 +19234,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="356" ht="12.8">
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K356" s="1"/>
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
@@ -19378,7 +19483,7 @@
       <c r="IV356" s="1"/>
       <c r="IW356" s="1"/>
     </row>
-    <row r="357" ht="12.8">
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K357" s="1"/>
       <c r="L357" s="1"/>
       <c r="M357" s="1"/>
@@ -19627,7 +19732,7 @@
       <c r="IV357" s="1"/>
       <c r="IW357" s="1"/>
     </row>
-    <row r="358" ht="12.8">
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K358" s="1"/>
       <c r="L358" s="1"/>
       <c r="M358" s="1"/>
@@ -19876,7 +19981,7 @@
       <c r="IV358" s="1"/>
       <c r="IW358" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="1" ht="12.8">
+    <row r="366" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -20135,7 +20240,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="368" ht="12.8">
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K368" s="1"/>
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
@@ -20384,7 +20489,7 @@
       <c r="IV368" s="1"/>
       <c r="IW368" s="1"/>
     </row>
-    <row r="369" ht="12.8">
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K369" s="1"/>
       <c r="L369" s="1"/>
       <c r="M369" s="1"/>
@@ -20633,7 +20738,7 @@
       <c r="IV369" s="1"/>
       <c r="IW369" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="1" ht="12.8">
+    <row r="411" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -20892,7 +20997,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="413" ht="12.8">
+    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K413" s="1"/>
       <c r="L413" s="1"/>
       <c r="M413" s="1"/>
@@ -21141,7 +21246,7 @@
       <c r="IV413" s="1"/>
       <c r="IW413" s="1"/>
     </row>
-    <row r="414" ht="12.8">
+    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K414" s="1"/>
       <c r="L414" s="1"/>
       <c r="M414" s="1"/>
@@ -21390,7 +21495,7 @@
       <c r="IV414" s="1"/>
       <c r="IW414" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="1" ht="12.8">
+    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -21649,7 +21754,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="1" ht="12.8">
+    <row r="416" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -21908,7 +22013,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="417" ht="12.8">
+    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K417" s="1"/>
       <c r="L417" s="1"/>
       <c r="M417" s="1"/>
@@ -22157,7 +22262,7 @@
       <c r="IV417" s="1"/>
       <c r="IW417" s="1"/>
     </row>
-    <row r="418" ht="12.8">
+    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K418" s="1"/>
       <c r="L418" s="1"/>
       <c r="M418" s="1"/>
@@ -22406,7 +22511,7 @@
       <c r="IV418" s="1"/>
       <c r="IW418" s="1"/>
     </row>
-    <row r="419" ht="12.8">
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K419" s="1"/>
       <c r="L419" s="1"/>
       <c r="M419" s="1"/>
@@ -22655,7 +22760,7 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="1" ht="12.8">
+    <row r="429" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -22914,7 +23019,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="1" ht="12.8">
+    <row r="430" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -23173,7 +23278,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="431" ht="12.8">
+    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K431" s="1"/>
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
@@ -23422,7 +23527,7 @@
       <c r="IV431" s="1"/>
       <c r="IW431" s="1"/>
     </row>
-    <row r="432" ht="12.8">
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K432" s="1"/>
       <c r="L432" s="1"/>
       <c r="M432" s="1"/>
@@ -23671,7 +23776,7 @@
       <c r="IV432" s="1"/>
       <c r="IW432" s="1"/>
     </row>
-    <row r="433" ht="12.8">
+    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K433" s="1"/>
       <c r="L433" s="1"/>
       <c r="M433" s="1"/>
@@ -23920,7 +24025,7 @@
       <c r="IV433" s="1"/>
       <c r="IW433" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="1" ht="12.8">
+    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -24179,7 +24284,7 @@
       <c r="IV439" s="1"/>
       <c r="IW439" s="1"/>
     </row>
-    <row r="441" ht="12.8">
+    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K441" s="1"/>
       <c r="L441" s="1"/>
       <c r="M441" s="1"/>
@@ -24428,7 +24533,7 @@
       <c r="IV441" s="1"/>
       <c r="IW441" s="1"/>
     </row>
-    <row r="442" ht="12.8">
+    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K442" s="1"/>
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
@@ -24679,12 +24784,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -24692,24 +24797,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW439"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="7" width="48.94"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24740,17 +24846,17 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -24758,24 +24864,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -24783,13 +24892,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
-      <c r="K10" s="1"/>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K10" s="9"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -25037,37 +25146,37 @@
       <c r="IV10" s="1"/>
       <c r="IW10" s="1"/>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="n">
         <v>123</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="1"/>
+      <c r="K15" s="9"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -25315,20 +25424,22 @@
       <c r="IV15" s="1"/>
       <c r="IW15" s="1"/>
     </row>
-    <row r="16" ht="43.25">
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -25576,371 +25687,410 @@
       <c r="IV16" s="1"/>
       <c r="IW16" s="1"/>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="1" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="85.05">
+    <row r="34" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F34" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="36" ht="53.7">
+    <row r="36" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F36" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D47" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" ht="12.8">
-      <c r="A41" s="1" t="s">
-        <v>83</v>
+    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F51" s="1" t="s">
+        <v>81</v>
       </c>
-    </row>
-    <row r="42" ht="12.8">
-      <c r="H42" s="1">
-        <v>8</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" ht="12.8">
-      <c r="D43" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
-      <c r="D44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" ht="12.8">
-      <c r="D47" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" ht="12.8">
-      <c r="A49" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" ht="12.8">
-      <c r="D50" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" ht="53.7">
-      <c r="F51" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H51" s="1">
+      <c r="H51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="52" ht="12.8">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="53" ht="12.8">
-      <c r="H53" s="1">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D54" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="55" ht="43.25">
+    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F55" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>93</v>
+        <v>106</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="56" ht="12.8">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="57" ht="12.8">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>99</v>
+        <v>114</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="58" ht="12.8">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
-      <c r="J58" s="6" t="s">
-        <v>102</v>
+      <c r="J58" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
-      <c r="J59" s="6" t="s">
-        <v>104</v>
+      <c r="J59" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="61" s="3" customFormat="1" ht="12.8">
+    <row r="61" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -25951,7 +26101,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="K61" s="9"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -26199,25 +26349,28 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" ht="12.8">
-      <c r="H62" s="1">
+    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I62" s="7" t="s">
-        <v>105</v>
+      <c r="I62" s="12" t="s">
+        <v>123</v>
       </c>
-      <c r="J62" s="6" t="s">
-        <v>106</v>
+      <c r="J62" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="63" ht="12.8">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="65" s="5" customFormat="1" ht="12.8">
+    <row r="65" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -26228,7 +26381,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
+      <c r="K65" s="9"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
@@ -26476,100 +26629,103 @@
       <c r="IV65" s="1"/>
       <c r="IW65" s="1"/>
     </row>
-    <row r="66" ht="12.8">
-      <c r="H66" s="1">
+    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I66" s="7" t="s">
-        <v>108</v>
+      <c r="I66" s="12" t="s">
+        <v>127</v>
       </c>
-      <c r="J66" s="6" t="s">
-        <v>109</v>
+      <c r="J66" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D71" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="72" ht="12.8">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D72" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="6"/>
+      <c r="I72" s="11"/>
     </row>
-    <row r="73" ht="12.8">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I73" s="11"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="11"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D75" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I75" s="11"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I73" s="6"/>
     </row>
-    <row r="74" ht="12.8">
-      <c r="D74" s="1" t="s">
-        <v>68</v>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="1" t="s">
+        <v>134</v>
       </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="I74" s="6"/>
-    </row>
-    <row r="75" ht="12.8">
-      <c r="D75" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I75" s="6"/>
-    </row>
-    <row r="76" ht="12.8">
-      <c r="B76" s="1" t="s">
-        <v>45</v>
+      <c r="C80" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="79" ht="12.8">
-      <c r="A79" s="1" t="s">
-        <v>97</v>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="80" ht="12.8">
-      <c r="B80" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>115</v>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="81" ht="12.8">
-      <c r="B81" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" ht="12.8">
-      <c r="A84" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" s="3" customFormat="1" ht="12.8">
+    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -26577,16 +26733,18 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1">
+      <c r="H85" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
-      <c r="K85" s="1"/>
+      <c r="K85" s="13" t="s">
+        <v>138</v>
+      </c>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
@@ -26834,12 +26992,12 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="86" ht="12.8">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="89" s="5" customFormat="1" ht="12.8">
+    <row r="89" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -26850,7 +27008,7 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
+      <c r="K89" s="9"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
@@ -27098,7 +27256,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="1" ht="12.8">
+    <row r="99" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -27109,7 +27267,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
+      <c r="K99" s="9"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
@@ -27357,7 +27515,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="1" ht="12.8">
+    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -27368,7 +27526,7 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
+      <c r="K117" s="9"/>
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
@@ -27616,7 +27774,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="1" ht="12.8">
+    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -27627,7 +27785,7 @@
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
-      <c r="K118" s="1"/>
+      <c r="K118" s="9"/>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -27875,7 +28033,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="1" ht="12.8">
+    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -27886,7 +28044,7 @@
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
-      <c r="K119" s="1"/>
+      <c r="K119" s="9"/>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
@@ -28134,7 +28292,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="1" ht="12.8">
+    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -28145,7 +28303,7 @@
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
+      <c r="K126" s="9"/>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
@@ -28393,7 +28551,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="1" ht="12.8">
+    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -28404,7 +28562,7 @@
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
-      <c r="K127" s="1"/>
+      <c r="K127" s="9"/>
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
@@ -28652,7 +28810,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="1" ht="12.8">
+    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -28663,7 +28821,7 @@
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
-      <c r="K128" s="1"/>
+      <c r="K128" s="9"/>
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
@@ -28911,7 +29069,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="1" ht="12.8">
+    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -28922,7 +29080,7 @@
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
-      <c r="K129" s="1"/>
+      <c r="K129" s="9"/>
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
@@ -29170,7 +29328,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="1" ht="12.8">
+    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -29181,7 +29339,7 @@
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
-      <c r="K130" s="1"/>
+      <c r="K130" s="9"/>
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
@@ -29429,7 +29587,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="1" ht="12.8">
+    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -29440,7 +29598,7 @@
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
-      <c r="K157" s="1"/>
+      <c r="K157" s="9"/>
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -29688,7 +29846,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="1" ht="12.8">
+    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -29699,7 +29857,7 @@
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
+      <c r="K160" s="9"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
@@ -29947,7 +30105,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="1" ht="12.8">
+    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -29958,7 +30116,7 @@
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
+      <c r="K161" s="9"/>
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
@@ -30206,7 +30364,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="1" ht="12.8">
+    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -30217,7 +30375,7 @@
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
       <c r="J236" s="1"/>
-      <c r="K236" s="1"/>
+      <c r="K236" s="9"/>
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
@@ -30465,7 +30623,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="1" ht="12.8">
+    <row r="240" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -30476,7 +30634,7 @@
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
       <c r="J240" s="1"/>
-      <c r="K240" s="1"/>
+      <c r="K240" s="9"/>
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
@@ -30724,7 +30882,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="1" ht="12.8">
+    <row r="272" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -30735,7 +30893,7 @@
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
       <c r="J272" s="1"/>
-      <c r="K272" s="1"/>
+      <c r="K272" s="9"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
@@ -30983,7 +31141,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="1" ht="12.8">
+    <row r="286" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -30994,7 +31152,7 @@
       <c r="H286" s="1"/>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
-      <c r="K286" s="1"/>
+      <c r="K286" s="9"/>
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
@@ -31242,7 +31400,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="1" ht="12.8">
+    <row r="287" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -31253,7 +31411,7 @@
       <c r="H287" s="1"/>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
-      <c r="K287" s="1"/>
+      <c r="K287" s="9"/>
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
@@ -31501,7 +31659,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="1" ht="12.8">
+    <row r="300" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -31512,7 +31670,7 @@
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
       <c r="J300" s="1"/>
-      <c r="K300" s="1"/>
+      <c r="K300" s="9"/>
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
@@ -31760,7 +31918,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="1" ht="12.8">
+    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -31771,7 +31929,7 @@
       <c r="H306" s="1"/>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
-      <c r="K306" s="1"/>
+      <c r="K306" s="9"/>
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
@@ -32019,7 +32177,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="1" ht="12.8">
+    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -32030,7 +32188,7 @@
       <c r="H313" s="1"/>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
-      <c r="K313" s="1"/>
+      <c r="K313" s="9"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
@@ -32278,7 +32436,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="1" ht="12.8">
+    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -32289,7 +32447,7 @@
       <c r="H337" s="1"/>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
-      <c r="K337" s="1"/>
+      <c r="K337" s="9"/>
       <c r="L337" s="1"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
@@ -32537,7 +32695,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="1" ht="12.8">
+    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -32548,7 +32706,7 @@
       <c r="H348" s="1"/>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
-      <c r="K348" s="1"/>
+      <c r="K348" s="9"/>
       <c r="L348" s="1"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
@@ -32796,7 +32954,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="1" ht="12.8">
+    <row r="354" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -32807,7 +32965,7 @@
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
-      <c r="K354" s="1"/>
+      <c r="K354" s="9"/>
       <c r="L354" s="1"/>
       <c r="M354" s="1"/>
       <c r="N354" s="1"/>
@@ -33055,7 +33213,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="1" ht="12.8">
+    <row r="355" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -33066,7 +33224,7 @@
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
-      <c r="K355" s="1"/>
+      <c r="K355" s="9"/>
       <c r="L355" s="1"/>
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
@@ -33314,7 +33472,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="1" ht="12.8">
+    <row r="366" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -33325,7 +33483,7 @@
       <c r="H366" s="1"/>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
-      <c r="K366" s="1"/>
+      <c r="K366" s="9"/>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
@@ -33573,7 +33731,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="1" ht="12.8">
+    <row r="411" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -33584,7 +33742,7 @@
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
       <c r="J411" s="1"/>
-      <c r="K411" s="1"/>
+      <c r="K411" s="9"/>
       <c r="L411" s="1"/>
       <c r="M411" s="1"/>
       <c r="N411" s="1"/>
@@ -33832,7 +33990,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="1" ht="12.8">
+    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -33843,7 +34001,7 @@
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
       <c r="J415" s="1"/>
-      <c r="K415" s="1"/>
+      <c r="K415" s="9"/>
       <c r="L415" s="1"/>
       <c r="M415" s="1"/>
       <c r="N415" s="1"/>
@@ -34091,7 +34249,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="1" ht="12.8">
+    <row r="416" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -34102,7 +34260,7 @@
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
       <c r="J416" s="1"/>
-      <c r="K416" s="1"/>
+      <c r="K416" s="9"/>
       <c r="L416" s="1"/>
       <c r="M416" s="1"/>
       <c r="N416" s="1"/>
@@ -34350,7 +34508,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="1" ht="12.8">
+    <row r="429" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -34361,7 +34519,7 @@
       <c r="H429" s="1"/>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
-      <c r="K429" s="1"/>
+      <c r="K429" s="9"/>
       <c r="L429" s="1"/>
       <c r="M429" s="1"/>
       <c r="N429" s="1"/>
@@ -34609,7 +34767,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="1" ht="12.8">
+    <row r="430" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -34620,7 +34778,7 @@
       <c r="H430" s="1"/>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
-      <c r="K430" s="1"/>
+      <c r="K430" s="9"/>
       <c r="L430" s="1"/>
       <c r="M430" s="1"/>
       <c r="N430" s="1"/>
@@ -34868,7 +35026,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="1" ht="12.8">
+    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -34879,7 +35037,7 @@
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
       <c r="J439" s="1"/>
-      <c r="K439" s="1"/>
+      <c r="K439" s="9"/>
       <c r="L439" s="1"/>
       <c r="M439" s="1"/>
       <c r="N439" s="1"/>
@@ -35129,21 +35287,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H11 H14 H72:H1048576 H36:H70 H24:H34">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H23 H12:H13">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H71">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/Mod_Korean/Lang/KR/Dialog/Drama/_adv.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/_adv.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="god" sheetId="1" state="visible" r:id="rId3"/>
@@ -152,8 +152,8 @@
 #god_benefit</t>
   </si>
   <si>
-    <t xml:space="preserve">당신은 제단에 다가가면서, 신들에 얽힌 여러 전승을 떠올렸다.
-■신앙 《#god_name》
+    <t xml:space="preserve">- 당신은 제단에 다가가면서, 신들에 얽힌 여러 전승을 떠올렸다.
+&lt;color=olive&gt; 《#god_name》 &lt;/color&gt;
 #god_desc
 #god_benefit</t>
   </si>
@@ -235,7 +235,7 @@
 The two stood in silence, hands entwined, and pledged their love to last forever.</t>
   </si>
   <si>
-    <t xml:space="preserve">시에라력 #1년 #2, #3에서, #4은(는) #5에게 프로포즈했다.
+    <t xml:space="preserve">시에라력 #1년 #2, #3에서, #4은(는) #5에게 프러포즈했다.
 두 사람은 조용히 손을 맞잡고, 영원한 사랑을 이곳에서 맹세했다.</t>
   </si>
   <si>
@@ -650,7 +650,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -671,27 +671,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -916,7 +904,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="29.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="29.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1414,7 +1402,7 @@
       <c r="J30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="4" t="s">
         <v>41</v>
       </c>
       <c r="L30" s="1"/>
@@ -1680,7 +1668,7 @@
       <c r="J31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="0" t="s">
+      <c r="K31" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1700,7 +1688,7 @@
       <c r="J32" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K32" s="0" t="s">
+      <c r="K32" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1730,7 +1718,7 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F37" s="1" t="s">
         <v>18</v>
       </c>
@@ -1743,7 +1731,7 @@
       <c r="J37" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K37" s="4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1756,7 +1744,6 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -2007,7 +1994,6 @@
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -2531,7 +2517,6 @@
       <c r="IW64" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
@@ -2780,7 +2765,6 @@
       <c r="IW66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -3028,7 +3012,7 @@
       <c r="IV67" s="1"/>
       <c r="IW67" s="1"/>
     </row>
-    <row r="68" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3288,7 +3272,6 @@
       <c r="IW68" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
@@ -3537,7 +3520,6 @@
       <c r="IW70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -4045,7 +4027,6 @@
       <c r="IW85" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
@@ -4294,7 +4275,6 @@
       <c r="IW87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
@@ -4542,7 +4522,7 @@
       <c r="IV88" s="1"/>
       <c r="IW88" s="1"/>
     </row>
-    <row r="89" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4802,7 +4782,6 @@
       <c r="IW89" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
@@ -5051,7 +5030,6 @@
       <c r="IW91" s="1"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
@@ -5299,7 +5277,7 @@
       <c r="IV92" s="1"/>
       <c r="IW92" s="1"/>
     </row>
-    <row r="99" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5559,7 +5537,6 @@
       <c r="IW99" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -5808,7 +5785,6 @@
       <c r="IW101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -6834,7 +6810,6 @@
       <c r="IW119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
@@ -7083,7 +7058,6 @@
       <c r="IW120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
@@ -7332,7 +7306,6 @@
       <c r="IW121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
@@ -8876,7 +8849,6 @@
       <c r="IW130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
@@ -9125,7 +9097,6 @@
       <c r="IW131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K132" s="1"/>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
@@ -9374,7 +9345,6 @@
       <c r="IW132" s="1"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
@@ -9882,7 +9852,6 @@
       <c r="IW157" s="1"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -10649,7 +10618,6 @@
       <c r="IW161" s="1"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
@@ -10898,7 +10866,6 @@
       <c r="IW162" s="1"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
@@ -11147,7 +11114,6 @@
       <c r="IW163" s="1"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K164" s="1"/>
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
@@ -11655,7 +11621,6 @@
       <c r="IW236" s="1"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K238" s="1"/>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
@@ -11904,7 +11869,6 @@
       <c r="IW238" s="1"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K239" s="1"/>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
@@ -12152,7 +12116,7 @@
       <c r="IV239" s="1"/>
       <c r="IW239" s="1"/>
     </row>
-    <row r="240" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -12412,7 +12376,6 @@
       <c r="IW240" s="1"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K242" s="1"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
@@ -12661,7 +12624,6 @@
       <c r="IW242" s="1"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K243" s="1"/>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
@@ -12909,7 +12871,7 @@
       <c r="IV243" s="1"/>
       <c r="IW243" s="1"/>
     </row>
-    <row r="272" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -13169,7 +13131,6 @@
       <c r="IW272" s="1"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
@@ -13418,7 +13379,6 @@
       <c r="IW274" s="1"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
@@ -13666,7 +13626,7 @@
       <c r="IV275" s="1"/>
       <c r="IW275" s="1"/>
     </row>
-    <row r="286" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -13925,7 +13885,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -14185,7 +14145,6 @@
       <c r="IW287" s="1"/>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K288" s="1"/>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
@@ -14434,7 +14393,6 @@
       <c r="IW288" s="1"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K289" s="1"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
@@ -14683,7 +14641,6 @@
       <c r="IW289" s="1"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K290" s="1"/>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
@@ -14931,7 +14888,7 @@
       <c r="IV290" s="1"/>
       <c r="IW290" s="1"/>
     </row>
-    <row r="300" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -15191,7 +15148,6 @@
       <c r="IW300" s="1"/>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
@@ -15440,7 +15396,6 @@
       <c r="IW302" s="1"/>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
@@ -15948,7 +15903,6 @@
       <c r="IW306" s="1"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K308" s="1"/>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
@@ -16197,7 +16151,6 @@
       <c r="IW308" s="1"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
@@ -16705,7 +16658,6 @@
       <c r="IW313" s="1"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
@@ -16954,7 +16906,6 @@
       <c r="IW315" s="1"/>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K316" s="1"/>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
@@ -17462,7 +17413,6 @@
       <c r="IW337" s="1"/>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
@@ -17711,7 +17661,6 @@
       <c r="IW339" s="1"/>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
@@ -18219,7 +18168,6 @@
       <c r="IW348" s="1"/>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K350" s="1"/>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
       <c r="N350" s="1"/>
@@ -18468,7 +18416,6 @@
       <c r="IW350" s="1"/>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K351" s="1"/>
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
       <c r="N351" s="1"/>
@@ -18716,7 +18663,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="354" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -18975,7 +18922,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -19235,7 +19182,6 @@
       <c r="IW355" s="1"/>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K356" s="1"/>
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
       <c r="N356" s="1"/>
@@ -19484,7 +19430,6 @@
       <c r="IW356" s="1"/>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K357" s="1"/>
       <c r="L357" s="1"/>
       <c r="M357" s="1"/>
       <c r="N357" s="1"/>
@@ -19733,7 +19678,6 @@
       <c r="IW357" s="1"/>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K358" s="1"/>
       <c r="L358" s="1"/>
       <c r="M358" s="1"/>
       <c r="N358" s="1"/>
@@ -19981,7 +19925,7 @@
       <c r="IV358" s="1"/>
       <c r="IW358" s="1"/>
     </row>
-    <row r="366" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -20241,7 +20185,6 @@
       <c r="IW366" s="1"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K368" s="1"/>
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
       <c r="N368" s="1"/>
@@ -20490,7 +20433,6 @@
       <c r="IW368" s="1"/>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K369" s="1"/>
       <c r="L369" s="1"/>
       <c r="M369" s="1"/>
       <c r="N369" s="1"/>
@@ -20738,7 +20680,7 @@
       <c r="IV369" s="1"/>
       <c r="IW369" s="1"/>
     </row>
-    <row r="411" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -20998,7 +20940,6 @@
       <c r="IW411" s="1"/>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K413" s="1"/>
       <c r="L413" s="1"/>
       <c r="M413" s="1"/>
       <c r="N413" s="1"/>
@@ -21247,7 +21188,6 @@
       <c r="IW413" s="1"/>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K414" s="1"/>
       <c r="L414" s="1"/>
       <c r="M414" s="1"/>
       <c r="N414" s="1"/>
@@ -21754,7 +21694,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -22014,7 +21954,6 @@
       <c r="IW416" s="1"/>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K417" s="1"/>
       <c r="L417" s="1"/>
       <c r="M417" s="1"/>
       <c r="N417" s="1"/>
@@ -22263,7 +22202,6 @@
       <c r="IW417" s="1"/>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K418" s="1"/>
       <c r="L418" s="1"/>
       <c r="M418" s="1"/>
       <c r="N418" s="1"/>
@@ -22512,7 +22450,6 @@
       <c r="IW418" s="1"/>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K419" s="1"/>
       <c r="L419" s="1"/>
       <c r="M419" s="1"/>
       <c r="N419" s="1"/>
@@ -22760,7 +22697,7 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="429" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -23019,7 +22956,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -23279,7 +23216,6 @@
       <c r="IW430" s="1"/>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K431" s="1"/>
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
       <c r="N431" s="1"/>
@@ -23528,7 +23464,6 @@
       <c r="IW431" s="1"/>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K432" s="1"/>
       <c r="L432" s="1"/>
       <c r="M432" s="1"/>
       <c r="N432" s="1"/>
@@ -23777,7 +23712,6 @@
       <c r="IW432" s="1"/>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K433" s="1"/>
       <c r="L433" s="1"/>
       <c r="M433" s="1"/>
       <c r="N433" s="1"/>
@@ -24285,7 +24219,6 @@
       <c r="IW439" s="1"/>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K441" s="1"/>
       <c r="L441" s="1"/>
       <c r="M441" s="1"/>
       <c r="N441" s="1"/>
@@ -24534,7 +24467,6 @@
       <c r="IW441" s="1"/>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K442" s="1"/>
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
       <c r="N442" s="1"/>
@@ -24812,7 +24744,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="7" width="48.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="48.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24846,7 +24778,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -24880,7 +24812,7 @@
       <c r="J6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -24898,7 +24830,6 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K10" s="9"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -25176,7 +25107,6 @@
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="9"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -25437,7 +25367,7 @@
       <c r="J16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="6" t="s">
         <v>66</v>
       </c>
       <c r="L16" s="1"/>
@@ -25706,7 +25636,7 @@
       <c r="J17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="6" t="s">
         <v>70</v>
       </c>
     </row>
@@ -25822,7 +25752,7 @@
       <c r="J34" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="4" t="s">
         <v>84</v>
       </c>
     </row>
@@ -25847,7 +25777,7 @@
       <c r="J36" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K36" s="7" t="s">
+      <c r="K36" s="6" t="s">
         <v>88</v>
       </c>
     </row>
@@ -25867,7 +25797,7 @@
       <c r="J37" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K37" s="7" t="s">
+      <c r="K37" s="6" t="s">
         <v>92</v>
       </c>
     </row>
@@ -25887,7 +25817,7 @@
       <c r="J38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K38" s="7" t="s">
+      <c r="K38" s="6" t="s">
         <v>96</v>
       </c>
     </row>
@@ -25957,7 +25887,7 @@
       <c r="J51" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="K51" s="6" t="s">
         <v>101</v>
       </c>
     </row>
@@ -26004,7 +25934,7 @@
       <c r="J55" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="K55" s="7" t="s">
+      <c r="K55" s="6" t="s">
         <v>107</v>
       </c>
     </row>
@@ -26024,7 +25954,7 @@
       <c r="J56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="K56" s="6" t="s">
         <v>111</v>
       </c>
     </row>
@@ -26044,7 +25974,7 @@
       <c r="J57" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K57" s="7" t="s">
+      <c r="K57" s="6" t="s">
         <v>115</v>
       </c>
     </row>
@@ -26061,10 +25991,10 @@
       <c r="I58" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="K58" s="7" t="s">
+      <c r="K58" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -26081,10 +26011,10 @@
       <c r="I59" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="K59" s="7" t="s">
+      <c r="K59" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -26101,7 +26031,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="9"/>
+      <c r="K61" s="6"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -26353,13 +26283,13 @@
       <c r="H62" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="6" t="s">
         <v>125</v>
       </c>
     </row>
@@ -26368,7 +26298,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="65" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>116</v>
       </c>
@@ -26381,7 +26311,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="9"/>
+      <c r="K65" s="6"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
@@ -26629,17 +26559,17 @@
       <c r="IV65" s="1"/>
       <c r="IW65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H66" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="I66" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K66" s="7" t="s">
+      <c r="K66" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -26668,7 +26598,7 @@
       <c r="E72" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="11"/>
+      <c r="I72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="1" t="s">
@@ -26677,7 +26607,7 @@
       <c r="E73" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I73" s="11"/>
+      <c r="I73" s="8"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D74" s="1" t="s">
@@ -26686,7 +26616,7 @@
       <c r="E74" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="11"/>
+      <c r="I74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D75" s="1" t="s">
@@ -26695,7 +26625,7 @@
       <c r="E75" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I75" s="11"/>
+      <c r="I75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
@@ -26742,7 +26672,7 @@
       <c r="J85" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K85" s="13" t="s">
+      <c r="K85" s="10" t="s">
         <v>138</v>
       </c>
       <c r="L85" s="1"/>
@@ -26997,7 +26927,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -27008,7 +26938,7 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="9"/>
+      <c r="K89" s="6"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
@@ -27256,7 +27186,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="99" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -27267,7 +27197,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
-      <c r="K99" s="9"/>
+      <c r="K99" s="6"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
@@ -27526,7 +27456,7 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
-      <c r="K117" s="9"/>
+      <c r="K117" s="6"/>
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
@@ -27785,7 +27715,7 @@
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
-      <c r="K118" s="9"/>
+      <c r="K118" s="6"/>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -28044,7 +27974,7 @@
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
-      <c r="K119" s="9"/>
+      <c r="K119" s="6"/>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
@@ -28303,7 +28233,7 @@
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
-      <c r="K126" s="9"/>
+      <c r="K126" s="6"/>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
@@ -28562,7 +28492,7 @@
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
-      <c r="K127" s="9"/>
+      <c r="K127" s="6"/>
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
@@ -28821,7 +28751,7 @@
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
-      <c r="K128" s="9"/>
+      <c r="K128" s="6"/>
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
@@ -29080,7 +29010,7 @@
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
-      <c r="K129" s="9"/>
+      <c r="K129" s="6"/>
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
@@ -29339,7 +29269,7 @@
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
-      <c r="K130" s="9"/>
+      <c r="K130" s="6"/>
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
@@ -29598,7 +29528,7 @@
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
-      <c r="K157" s="9"/>
+      <c r="K157" s="6"/>
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -29857,7 +29787,7 @@
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
-      <c r="K160" s="9"/>
+      <c r="K160" s="6"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
@@ -30116,7 +30046,7 @@
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
-      <c r="K161" s="9"/>
+      <c r="K161" s="6"/>
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
@@ -30375,7 +30305,7 @@
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
       <c r="J236" s="1"/>
-      <c r="K236" s="9"/>
+      <c r="K236" s="6"/>
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
@@ -30623,7 +30553,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="240" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -30634,7 +30564,7 @@
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
       <c r="J240" s="1"/>
-      <c r="K240" s="9"/>
+      <c r="K240" s="6"/>
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
@@ -30882,7 +30812,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="272" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -30893,7 +30823,7 @@
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
       <c r="J272" s="1"/>
-      <c r="K272" s="9"/>
+      <c r="K272" s="6"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
@@ -31141,7 +31071,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="286" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -31152,7 +31082,7 @@
       <c r="H286" s="1"/>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
-      <c r="K286" s="9"/>
+      <c r="K286" s="6"/>
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
@@ -31400,7 +31330,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -31411,7 +31341,7 @@
       <c r="H287" s="1"/>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
-      <c r="K287" s="9"/>
+      <c r="K287" s="6"/>
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
@@ -31659,7 +31589,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="300" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -31670,7 +31600,7 @@
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
       <c r="J300" s="1"/>
-      <c r="K300" s="9"/>
+      <c r="K300" s="6"/>
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
@@ -31929,7 +31859,7 @@
       <c r="H306" s="1"/>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
-      <c r="K306" s="9"/>
+      <c r="K306" s="6"/>
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
@@ -32188,7 +32118,7 @@
       <c r="H313" s="1"/>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
-      <c r="K313" s="9"/>
+      <c r="K313" s="6"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
@@ -32447,7 +32377,7 @@
       <c r="H337" s="1"/>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
-      <c r="K337" s="9"/>
+      <c r="K337" s="6"/>
       <c r="L337" s="1"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
@@ -32706,7 +32636,7 @@
       <c r="H348" s="1"/>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
-      <c r="K348" s="9"/>
+      <c r="K348" s="6"/>
       <c r="L348" s="1"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
@@ -32954,7 +32884,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="354" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -32965,7 +32895,7 @@
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
-      <c r="K354" s="9"/>
+      <c r="K354" s="6"/>
       <c r="L354" s="1"/>
       <c r="M354" s="1"/>
       <c r="N354" s="1"/>
@@ -33213,7 +33143,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -33224,7 +33154,7 @@
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
-      <c r="K355" s="9"/>
+      <c r="K355" s="6"/>
       <c r="L355" s="1"/>
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
@@ -33472,7 +33402,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="366" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -33483,7 +33413,7 @@
       <c r="H366" s="1"/>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
-      <c r="K366" s="9"/>
+      <c r="K366" s="6"/>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
@@ -33731,7 +33661,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="411" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -33742,7 +33672,7 @@
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
       <c r="J411" s="1"/>
-      <c r="K411" s="9"/>
+      <c r="K411" s="6"/>
       <c r="L411" s="1"/>
       <c r="M411" s="1"/>
       <c r="N411" s="1"/>
@@ -34001,7 +33931,7 @@
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
       <c r="J415" s="1"/>
-      <c r="K415" s="9"/>
+      <c r="K415" s="6"/>
       <c r="L415" s="1"/>
       <c r="M415" s="1"/>
       <c r="N415" s="1"/>
@@ -34249,7 +34179,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -34260,7 +34190,7 @@
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
       <c r="J416" s="1"/>
-      <c r="K416" s="9"/>
+      <c r="K416" s="6"/>
       <c r="L416" s="1"/>
       <c r="M416" s="1"/>
       <c r="N416" s="1"/>
@@ -34508,7 +34438,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="429" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -34519,7 +34449,7 @@
       <c r="H429" s="1"/>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
-      <c r="K429" s="9"/>
+      <c r="K429" s="6"/>
       <c r="L429" s="1"/>
       <c r="M429" s="1"/>
       <c r="N429" s="1"/>
@@ -34767,7 +34697,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -34778,7 +34708,7 @@
       <c r="H430" s="1"/>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
-      <c r="K430" s="9"/>
+      <c r="K430" s="6"/>
       <c r="L430" s="1"/>
       <c r="M430" s="1"/>
       <c r="N430" s="1"/>
@@ -35037,7 +34967,7 @@
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
       <c r="J439" s="1"/>
-      <c r="K439" s="9"/>
+      <c r="K439" s="6"/>
       <c r="L439" s="1"/>
       <c r="M439" s="1"/>
       <c r="N439" s="1"/>

--- a/Mod_Korean/Lang/KR/Dialog/Drama/_adv.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/_adv.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="god" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="general" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="god" sheetId="1" r:id="rId3"/>
+    <sheet name="general" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="140">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -152,12 +152,6 @@
 #god_benefit</t>
   </si>
   <si>
-    <t xml:space="preserve">- 당신은 제단에 다가가면서, 신들에 얽힌 여러 전승을 떠올렸다.
-&lt;color=olive&gt; 《#god_name》 &lt;/color&gt;
-#god_desc
-#god_benefit</t>
-  </si>
-  <si>
     <t xml:space="preserve">worship2</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t xml:space="preserve">Worship #god_name.</t>
   </si>
   <si>
-    <t xml:space="preserve">#god_name을(를) 믿는다</t>
-  </si>
-  <si>
     <t xml:space="preserve">end</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
   </si>
   <si>
     <t xml:space="preserve">(Leave)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">떠난다</t>
   </si>
   <si>
     <t xml:space="preserve">cancel</t>
@@ -199,10 +187,6 @@
 "#godtalk_worship"</t>
   </si>
   <si>
-    <t xml:space="preserve">당신의 머릿속에 신비한 목소리가 울렸다.
-「#godtalk_worship」</t>
-  </si>
-  <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
@@ -210,9 +194,6 @@
   </si>
   <si>
     <t xml:space="preserve">Marriage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결혼</t>
   </si>
   <si>
     <t xml:space="preserve">marry</t>
@@ -235,10 +216,6 @@
 The two stood in silence, hands entwined, and pledged their love to last forever.</t>
   </si>
   <si>
-    <t xml:space="preserve">시에라력 #1년 #2, #3에서, #4은(는) #5에게 프러포즈했다.
-두 사람은 조용히 손을 맞잡고, 영원한 사랑을 이곳에서 맹세했다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">marry2</t>
   </si>
   <si>
@@ -246,9 +223,6 @@
   </si>
   <si>
     <t xml:space="preserve">Without you, life has no meaning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">평생을 당신에게 바친다</t>
   </si>
   <si>
     <t xml:space="preserve">invoke</t>
@@ -294,11 +268,6 @@
 When the moonlight spills down upon the earth, under an eternal vow, the two shall be firmly bound as one.</t>
   </si>
   <si>
-    <t xml:space="preserve">잠들지 않는 별들이여, 돌고 도는 달이여. 오늘 밤, 이 두 사람의 새로운 출발을 지켜보며 이 행운의 날을 축복하소서.
-밤하늘에 바쳐진 꽃다발이, 내일로 이어지는 입맞춤이, 머지않아 황금빛으로 빛나는 시간을 맺게 하리라.
-달빛이 지상으로 넘쳐흐르는 그 때, 영원한 맹세 아래 두 사람은 굳게 맺어지리라.</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.5,1</t>
   </si>
   <si>
@@ -310,10 +279,6 @@
 Do you swear to take #tg as your lifelong partner, to never let go of #tg_his hand in joyful mornings or tearful nights, and to remain by #tg_his side forever?</t>
   </si>
   <si>
-    <t xml:space="preserve">#pc_full.
-그대는 #tg을(를) 평생의 반려로 맞아, 기쁨의 아침에도, 눈물의 밤에도, 그 손을 놓지 않고 영원히 그 곁을 지킬 것을 맹세하는가?</t>
-  </si>
-  <si>
     <t xml:space="preserve">wedding2</t>
   </si>
   <si>
@@ -323,9 +288,6 @@
     <t xml:space="preserve">Yes.</t>
   </si>
   <si>
-    <t xml:space="preserve">네</t>
-  </si>
-  <si>
     <t xml:space="preserve">wedding_fail</t>
   </si>
   <si>
@@ -333,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">아니요</t>
   </si>
   <si>
     <t xml:space="preserve">…</t>
@@ -352,17 +311,10 @@
 Do you swear to take #pc_full as your one and only partner, to entrust your heart through storms of fate and in peaceful slumber, and to walk together always?</t>
   </si>
   <si>
-    <t xml:space="preserve">#tg.
-그대는 #pc_full을(를) 유일한 반려로 맞아, 운명의 폭풍 속에서도, 고요한 잠에 들면서도, 그 마음을 맡기고 함께 걸어나갈 것을 맹세하는가?</t>
-  </si>
-  <si>
     <t xml:space="preserve">…はい。</t>
   </si>
   <si>
     <t xml:space="preserve">...Yes, I do.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…네.</t>
   </si>
   <si>
     <t xml:space="preserve">星々の証人のもと、これにて二人はひとつに結ばれた。汝らに幸運の女神の祝福あれ…！ 
@@ -371,29 +323,6 @@
   <si>
     <t xml:space="preserve">Before the witness of the stars, these two are now united as one. May the goddess of fortune bless you both!
 Now... the kiss of your vow.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">별들의 증언 아래, 이로써 두 사람은 하나로 맺어졌다. 그대들에게 행운의 여신의 축복 있으라</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">…!
-이제… 맹세의 입맞춤을.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">wedding3</t>
@@ -405,9 +334,6 @@
     <t xml:space="preserve">(Kiss #tg_him)</t>
   </si>
   <si>
-    <t xml:space="preserve">맹세의 입맞춤을 한다</t>
-  </si>
-  <si>
     <t xml:space="preserve">wedding5</t>
   </si>
   <si>
@@ -415,9 +341,6 @@
   </si>
   <si>
     <t xml:space="preserve">(Make love with #tg_him)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기분 좋은 일을 한다</t>
   </si>
   <si>
     <t xml:space="preserve">wedding4</t>
@@ -429,16 +352,10 @@
     <t xml:space="preserve">(Blush and stay silent)</t>
   </si>
   <si>
-    <t xml:space="preserve">부끄러워서 입을 다문다</t>
-  </si>
-  <si>
     <t xml:space="preserve">逃げる</t>
   </si>
   <si>
     <t xml:space="preserve">(Run away)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도망간다</t>
   </si>
   <si>
     <r>
@@ -474,9 +391,6 @@
   </si>
   <si>
     <t xml:space="preserve">(#tg smiles shyly and quietly presses #tg_his lip to yours.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#tg은(는) 부끄러운 듯 미소짓고 당신과 조용히 입을 맞추었다)</t>
   </si>
   <si>
     <t xml:space="preserve">wedding_fin</t>
@@ -517,9 +431,6 @@
     <t xml:space="preserve">(#tg lets out a soft laugh and gently brings #tg_his lip to yours.) </t>
   </si>
   <si>
-    <t xml:space="preserve">(#tg은(는) 가볍게 웃음짓고는 당신과 살며시 입을 맞추었다)</t>
-  </si>
-  <si>
     <t xml:space="preserve">clap3</t>
   </si>
   <si>
@@ -544,6 +455,79 @@
     <t xml:space="preserve">What?</t>
   </si>
   <si>
+    <t xml:space="preserve">- 당신은 제단에 다가가면서, 신들에 얽힌 여러 전승을 떠올렸다.
+&lt;color=olive&gt; 《#god_name》 &lt;/color&gt;
+#god_desc
+#god_benefit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#god_name을(를) 믿는다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">떠난다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">당신의 머릿속에 신비한 목소리가 울렸다.
+「#godtalk_worship」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결혼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시에라력 #1년 #2, #3에서, #4은(는) #5에게 프러포즈했다.
+두 사람은 조용히 손을 맞잡고, 영원한 사랑을 이곳에서 맹세했다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">평생을 당신에게 바친다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">잠들지 않는 별들이여, 돌고 도는 달이여. 오늘 밤, 이 두 사람의 새로운 출발을 지켜보며 이 행운의 날을 축복하소서.
+밤하늘에 바쳐진 꽃다발이, 내일로 이어지는 입맞춤이, 머지않아 황금빛으로 빛나는 시간을 맺게 하리라.
+달빛이 지상으로 넘쳐흐르는 그 때, 영원한 맹세 아래 두 사람은 굳게 맺어지리라.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#pc_full.
+그대는 #tg을(를) 평생의 반려로 맞아, 기쁨의 아침에도, 눈물의 밤에도, 그 손을 놓지 않고 영원히 그 곁을 지킬 것을 맹세하는가?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아니요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#tg.
+그대는 #pc_full을(를) 유일한 반려로 맞아, 운명의 폭풍 속에서도, 고요한 잠에 들면서도, 그 마음을 맡기고 함께 걸어나갈 것을 맹세하는가?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…네.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">별들의 증언 아래, 이로써 두 사람은 하나로 맺어졌다. 그대들에게 행운의 여신의 축복 있으라…!
+이제… 맹세의 입맞춤을.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맹세의 입맞춤을 한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기분 좋은 일을 한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부끄러워서 입을 다문다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도망간다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg은(는) 부끄러운 듯 미소짓고 당신과 조용히 입을 맞추었다)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#tg은(는) 가볍게 웃음짓고는 당신과 살며시 입을 맞추었다)</t>
+  </si>
+  <si>
     <t xml:space="preserve">…에?</t>
   </si>
 </sst>
@@ -555,7 +539,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -566,33 +550,26 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <family/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <family/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="129"/>
+      <family/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -617,7 +594,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -626,74 +603,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="8">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -707,13 +672,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -790,37 +755,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -889,25 +854,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IW442"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="29.34"/>
+    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -942,13 +906,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -956,7 +920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
@@ -964,7 +928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -972,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
@@ -980,7 +944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,7 +952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -996,7 +960,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1004,7 +968,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1012,7 +976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,7 +984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1028,7 +992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1036,7 +1000,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1044,7 +1008,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1052,7 +1016,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="D18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1060,7 +1024,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1068,7 +1032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1076,7 +1040,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1084,7 +1048,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,7 +1056,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1100,7 +1064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1108,17 +1072,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1126,7 +1090,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="3" customFormat="1" ht="12.8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1389,11 +1353,11 @@
       <c r="IV29" s="1"/>
       <c r="IW29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="74.6">
       <c r="F30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -1402,8 +1366,8 @@
       <c r="J30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K30" s="4" t="s">
-        <v>41</v>
+      <c r="K30" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -1652,98 +1616,99 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="B31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="1">
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
+      <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>46</v>
+      <c r="D32" s="1" t="s">
+        <v>42</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="1">
         <v>3</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
+      <c r="D33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>50</v>
-      </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D33" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="D36" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="32.8">
       <c r="F37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="1">
         <v>4</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
-      <c r="K37" s="4" t="s">
-        <v>55</v>
+      <c r="K37" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
+      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -1991,9 +1956,10 @@
       <c r="IV40" s="1"/>
       <c r="IW40" s="1"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
+      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -2241,23 +2207,23 @@
       <c r="IV44" s="1"/>
       <c r="IW44" s="1"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="64" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="3" customFormat="1" ht="12.8">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2516,7 +2482,8 @@
       <c r="IV64" s="1"/>
       <c r="IW64" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="12.8">
+      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
@@ -2764,7 +2731,8 @@
       <c r="IV66" s="1"/>
       <c r="IW66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
+      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -3012,7 +2980,7 @@
       <c r="IV67" s="1"/>
       <c r="IW67" s="1"/>
     </row>
-    <row r="68" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="5" customFormat="1" ht="12.8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3271,7 +3239,8 @@
       <c r="IV68" s="1"/>
       <c r="IW68" s="1"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
@@ -3519,7 +3488,8 @@
       <c r="IV70" s="1"/>
       <c r="IW70" s="1"/>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
+      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -3767,7 +3737,7 @@
       <c r="IV71" s="1"/>
       <c r="IW71" s="1"/>
     </row>
-    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="3" customFormat="1" ht="12.8">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4026,7 +3996,8 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
+      <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
@@ -4274,7 +4245,8 @@
       <c r="IV87" s="1"/>
       <c r="IW87" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="12.8">
+      <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
@@ -4522,7 +4494,7 @@
       <c r="IV88" s="1"/>
       <c r="IW88" s="1"/>
     </row>
-    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="5" customFormat="1" ht="12.8">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4781,7 +4753,8 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.8">
+      <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
@@ -5029,7 +5002,8 @@
       <c r="IV91" s="1"/>
       <c r="IW91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.8">
+      <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
@@ -5277,7 +5251,7 @@
       <c r="IV92" s="1"/>
       <c r="IW92" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" s="5" customFormat="1" ht="12.8">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5536,7 +5510,8 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="12.8">
+      <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -5784,7 +5759,8 @@
       <c r="IV101" s="1"/>
       <c r="IW101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" ht="12.8">
+      <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -6032,7 +6008,7 @@
       <c r="IV102" s="1"/>
       <c r="IW102" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="3" customFormat="1" ht="12.8">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -6291,7 +6267,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="3" customFormat="1" ht="12.8">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -6550,7 +6526,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="3" customFormat="1" ht="12.8">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -6809,7 +6785,8 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" ht="12.8">
+      <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
@@ -7057,7 +7034,8 @@
       <c r="IV120" s="1"/>
       <c r="IW120" s="1"/>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="12.8">
+      <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
@@ -7305,7 +7283,8 @@
       <c r="IV121" s="1"/>
       <c r="IW121" s="1"/>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" ht="12.8">
+      <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
@@ -7553,7 +7532,7 @@
       <c r="IV122" s="1"/>
       <c r="IW122" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" s="3" customFormat="1" ht="12.8">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7812,7 +7791,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" s="3" customFormat="1" ht="12.8">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -8071,7 +8050,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" s="3" customFormat="1" ht="12.8">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -8330,7 +8309,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="3" customFormat="1" ht="12.8">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8589,7 +8568,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="3" customFormat="1" ht="12.8">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8848,7 +8827,8 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="12.8">
+      <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
@@ -9096,7 +9076,8 @@
       <c r="IV131" s="1"/>
       <c r="IW131" s="1"/>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="12.8">
+      <c r="K132" s="1"/>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
@@ -9344,7 +9325,8 @@
       <c r="IV132" s="1"/>
       <c r="IW132" s="1"/>
     </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" ht="12.8">
+      <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
@@ -9592,7 +9574,7 @@
       <c r="IV133" s="1"/>
       <c r="IW133" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="3" customFormat="1" ht="12.8">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -9851,7 +9833,8 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" ht="12.8">
+      <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -10099,7 +10082,7 @@
       <c r="IV159" s="1"/>
       <c r="IW159" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" s="3" customFormat="1" ht="12.8">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -10358,7 +10341,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="3" customFormat="1" ht="12.8">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -10617,7 +10600,8 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" ht="12.8">
+      <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
@@ -10865,7 +10849,8 @@
       <c r="IV162" s="1"/>
       <c r="IW162" s="1"/>
     </row>
-    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" ht="12.8">
+      <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
@@ -11113,7 +11098,8 @@
       <c r="IV163" s="1"/>
       <c r="IW163" s="1"/>
     </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" ht="12.8">
+      <c r="K164" s="1"/>
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
@@ -11361,7 +11347,7 @@
       <c r="IV164" s="1"/>
       <c r="IW164" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="3" customFormat="1" ht="12.8">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -11620,7 +11606,8 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" ht="12.8">
+      <c r="K238" s="1"/>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
@@ -11868,7 +11855,8 @@
       <c r="IV238" s="1"/>
       <c r="IW238" s="1"/>
     </row>
-    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" ht="12.8">
+      <c r="K239" s="1"/>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
@@ -12116,7 +12104,7 @@
       <c r="IV239" s="1"/>
       <c r="IW239" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="5" customFormat="1" ht="12.8">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -12375,7 +12363,8 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" ht="12.8">
+      <c r="K242" s="1"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
@@ -12623,7 +12612,8 @@
       <c r="IV242" s="1"/>
       <c r="IW242" s="1"/>
     </row>
-    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" ht="12.8">
+      <c r="K243" s="1"/>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
@@ -12871,7 +12861,7 @@
       <c r="IV243" s="1"/>
       <c r="IW243" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="1" ht="12.8">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -13130,7 +13120,8 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" ht="12.8">
+      <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
@@ -13378,7 +13369,8 @@
       <c r="IV274" s="1"/>
       <c r="IW274" s="1"/>
     </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" ht="12.8">
+      <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
@@ -13626,7 +13618,7 @@
       <c r="IV275" s="1"/>
       <c r="IW275" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="5" customFormat="1" ht="12.8">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -13885,7 +13877,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="1" ht="12.8">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -14144,7 +14136,8 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" ht="12.8">
+      <c r="K288" s="1"/>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
@@ -14392,7 +14385,8 @@
       <c r="IV288" s="1"/>
       <c r="IW288" s="1"/>
     </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" ht="12.8">
+      <c r="K289" s="1"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
@@ -14640,7 +14634,8 @@
       <c r="IV289" s="1"/>
       <c r="IW289" s="1"/>
     </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" ht="12.8">
+      <c r="K290" s="1"/>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
@@ -14888,7 +14883,7 @@
       <c r="IV290" s="1"/>
       <c r="IW290" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="5" customFormat="1" ht="12.8">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -15147,7 +15142,8 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" ht="12.8">
+      <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
@@ -15395,7 +15391,8 @@
       <c r="IV302" s="1"/>
       <c r="IW302" s="1"/>
     </row>
-    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" ht="12.8">
+      <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
@@ -15643,7 +15640,7 @@
       <c r="IV303" s="1"/>
       <c r="IW303" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="3" customFormat="1" ht="12.8">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -15902,7 +15899,8 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" ht="12.8">
+      <c r="K308" s="1"/>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
@@ -16150,7 +16148,8 @@
       <c r="IV308" s="1"/>
       <c r="IW308" s="1"/>
     </row>
-    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" ht="12.8">
+      <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
@@ -16398,7 +16397,7 @@
       <c r="IV309" s="1"/>
       <c r="IW309" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="3" customFormat="1" ht="12.8">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -16657,7 +16656,8 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" ht="12.8">
+      <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
@@ -16905,7 +16905,8 @@
       <c r="IV315" s="1"/>
       <c r="IW315" s="1"/>
     </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" ht="12.8">
+      <c r="K316" s="1"/>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
@@ -17153,7 +17154,7 @@
       <c r="IV316" s="1"/>
       <c r="IW316" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="3" customFormat="1" ht="12.8">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -17412,7 +17413,8 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" ht="12.8">
+      <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
@@ -17660,7 +17662,8 @@
       <c r="IV339" s="1"/>
       <c r="IW339" s="1"/>
     </row>
-    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" ht="12.8">
+      <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
@@ -17908,7 +17911,7 @@
       <c r="IV340" s="1"/>
       <c r="IW340" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="3" customFormat="1" ht="12.8">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -18167,7 +18170,8 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" ht="12.8">
+      <c r="K350" s="1"/>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
       <c r="N350" s="1"/>
@@ -18415,7 +18419,8 @@
       <c r="IV350" s="1"/>
       <c r="IW350" s="1"/>
     </row>
-    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" ht="12.8">
+      <c r="K351" s="1"/>
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
       <c r="N351" s="1"/>
@@ -18663,7 +18668,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="5" customFormat="1" ht="12.8">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -18922,7 +18927,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="5" customFormat="1" ht="12.8">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -19181,7 +19186,8 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" ht="12.8">
+      <c r="K356" s="1"/>
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
       <c r="N356" s="1"/>
@@ -19429,7 +19435,8 @@
       <c r="IV356" s="1"/>
       <c r="IW356" s="1"/>
     </row>
-    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" ht="12.8">
+      <c r="K357" s="1"/>
       <c r="L357" s="1"/>
       <c r="M357" s="1"/>
       <c r="N357" s="1"/>
@@ -19677,7 +19684,8 @@
       <c r="IV357" s="1"/>
       <c r="IW357" s="1"/>
     </row>
-    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" ht="12.8">
+      <c r="K358" s="1"/>
       <c r="L358" s="1"/>
       <c r="M358" s="1"/>
       <c r="N358" s="1"/>
@@ -19925,7 +19933,7 @@
       <c r="IV358" s="1"/>
       <c r="IW358" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="5" customFormat="1" ht="12.8">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -20184,7 +20192,8 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" ht="12.8">
+      <c r="K368" s="1"/>
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
       <c r="N368" s="1"/>
@@ -20432,7 +20441,8 @@
       <c r="IV368" s="1"/>
       <c r="IW368" s="1"/>
     </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" ht="12.8">
+      <c r="K369" s="1"/>
       <c r="L369" s="1"/>
       <c r="M369" s="1"/>
       <c r="N369" s="1"/>
@@ -20680,7 +20690,7 @@
       <c r="IV369" s="1"/>
       <c r="IW369" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="1" ht="12.8">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -20939,7 +20949,8 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" ht="12.8">
+      <c r="K413" s="1"/>
       <c r="L413" s="1"/>
       <c r="M413" s="1"/>
       <c r="N413" s="1"/>
@@ -21187,7 +21198,8 @@
       <c r="IV413" s="1"/>
       <c r="IW413" s="1"/>
     </row>
-    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" ht="12.8">
+      <c r="K414" s="1"/>
       <c r="L414" s="1"/>
       <c r="M414" s="1"/>
       <c r="N414" s="1"/>
@@ -21435,7 +21447,7 @@
       <c r="IV414" s="1"/>
       <c r="IW414" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" s="3" customFormat="1" ht="12.8">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -21694,7 +21706,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="5" customFormat="1" ht="12.8">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -21953,7 +21965,8 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" ht="12.8">
+      <c r="K417" s="1"/>
       <c r="L417" s="1"/>
       <c r="M417" s="1"/>
       <c r="N417" s="1"/>
@@ -22201,7 +22214,8 @@
       <c r="IV417" s="1"/>
       <c r="IW417" s="1"/>
     </row>
-    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" ht="12.8">
+      <c r="K418" s="1"/>
       <c r="L418" s="1"/>
       <c r="M418" s="1"/>
       <c r="N418" s="1"/>
@@ -22449,7 +22463,8 @@
       <c r="IV418" s="1"/>
       <c r="IW418" s="1"/>
     </row>
-    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" ht="12.8">
+      <c r="K419" s="1"/>
       <c r="L419" s="1"/>
       <c r="M419" s="1"/>
       <c r="N419" s="1"/>
@@ -22697,7 +22712,7 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="1" ht="12.8">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -22956,7 +22971,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="1" ht="12.8">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -23215,7 +23230,8 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" ht="12.8">
+      <c r="K431" s="1"/>
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
       <c r="N431" s="1"/>
@@ -23463,7 +23479,8 @@
       <c r="IV431" s="1"/>
       <c r="IW431" s="1"/>
     </row>
-    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" ht="12.8">
+      <c r="K432" s="1"/>
       <c r="L432" s="1"/>
       <c r="M432" s="1"/>
       <c r="N432" s="1"/>
@@ -23711,7 +23728,8 @@
       <c r="IV432" s="1"/>
       <c r="IW432" s="1"/>
     </row>
-    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" ht="12.8">
+      <c r="K433" s="1"/>
       <c r="L433" s="1"/>
       <c r="M433" s="1"/>
       <c r="N433" s="1"/>
@@ -23959,7 +23977,7 @@
       <c r="IV433" s="1"/>
       <c r="IW433" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" s="3" customFormat="1" ht="12.8">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -24218,7 +24236,8 @@
       <c r="IV439" s="1"/>
       <c r="IW439" s="1"/>
     </row>
-    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" ht="12.8">
+      <c r="K441" s="1"/>
       <c r="L441" s="1"/>
       <c r="M441" s="1"/>
       <c r="N441" s="1"/>
@@ -24466,7 +24485,8 @@
       <c r="IV441" s="1"/>
       <c r="IW441" s="1"/>
     </row>
-    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" ht="12.8">
+      <c r="K442" s="1"/>
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
       <c r="N442" s="1"/>
@@ -24716,12 +24736,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -24729,25 +24749,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IW439"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="48.93"/>
+    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24778,17 +24797,17 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -24796,27 +24815,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="1">
         <v>3</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>59</v>
+      <c r="K6" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -24824,12 +24843,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -25077,36 +25097,37 @@
       <c r="IV10" s="1"/>
       <c r="IW10" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="1">
         <v>123</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -25354,21 +25375,21 @@
       <c r="IV15" s="1"/>
       <c r="IW15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="43.25">
       <c r="F16" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>66</v>
+      <c r="K16" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -25617,410 +25638,410 @@
       <c r="IV16" s="1"/>
       <c r="IW16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="1">
         <v>2</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
-      <c r="K17" s="6" t="s">
-        <v>70</v>
+      <c r="K17" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="D25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="D26" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="D27" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
+      <c r="D29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
+      <c r="D30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" ht="12.8">
+      <c r="D31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
+      <c r="D32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
+      <c r="D33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="85.05">
+      <c r="F34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" s="1">
+        <v>4</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>76</v>
       </c>
+      <c r="K34" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="1" t="s">
-        <v>71</v>
+    <row r="35" ht="12.8">
+      <c r="D35" s="1" t="s">
+        <v>73</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="1" t="s">
+    <row r="36" ht="53.7">
+      <c r="F36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" s="1">
+        <v>5</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="J36" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>4</v>
+      <c r="K36" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D32" s="1" t="s">
-        <v>75</v>
+    <row r="37" ht="12.8">
+      <c r="B37" s="1" t="s">
+        <v>80</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="D37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="1">
+        <v>6</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
+      <c r="B38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H38" s="1">
+        <v>7</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" ht="12.8">
+      <c r="A41" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
+      <c r="H42" s="1">
+        <v>8</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" ht="12.8">
+      <c r="D43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D33" s="1" t="s">
+    <row r="44" ht="12.8">
+      <c r="D44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" ht="12.8">
+      <c r="D47" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" ht="12.8">
+      <c r="A49" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>1</v>
+    </row>
+    <row r="50" ht="12.8">
+      <c r="D50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="1" t="s">
-        <v>81</v>
+    <row r="51" ht="53.7">
+      <c r="F51" s="1" t="s">
+        <v>74</v>
       </c>
-      <c r="H34" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H42" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D47" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D50" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F51" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="1">
         <v>9</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
-      <c r="K51" s="6" t="s">
-        <v>101</v>
+      <c r="K51" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.8">
       <c r="D52" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H53" s="1" t="n">
+    <row r="53" ht="12.8">
+      <c r="H53" s="1">
         <v>10</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>104</v>
+      <c r="K53" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="D54" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="43.25">
       <c r="F55" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="H55" s="1">
         <v>11</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>107</v>
+      <c r="K55" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="12.8">
       <c r="B56" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="1">
         <v>12</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>111</v>
+      <c r="K56" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="12.8">
       <c r="B57" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="1">
         <v>13</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
-      <c r="K57" s="6" t="s">
-        <v>115</v>
+      <c r="K57" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.8">
       <c r="B58" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="1">
         <v>14</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
-      <c r="J58" s="8" t="s">
-        <v>118</v>
+      <c r="J58" s="6" t="s">
+        <v>102</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>119</v>
+      <c r="K58" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="B59" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="1">
         <v>15</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
-      <c r="J59" s="8" t="s">
-        <v>121</v>
+      <c r="J59" s="6" t="s">
+        <v>104</v>
       </c>
-      <c r="K59" s="6" t="s">
-        <v>122</v>
+      <c r="K59" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="61" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="3" customFormat="1" ht="12.8">
       <c r="A61" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -26031,7 +26052,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="6"/>
+      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -26279,28 +26300,28 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H62" s="1" t="n">
+    <row r="62" ht="12.8">
+      <c r="H62" s="1">
         <v>16</v>
       </c>
-      <c r="I62" s="9" t="s">
-        <v>123</v>
+      <c r="I62" s="7" t="s">
+        <v>105</v>
       </c>
-      <c r="J62" s="8" t="s">
-        <v>124</v>
+      <c r="J62" s="6" t="s">
+        <v>106</v>
       </c>
-      <c r="K62" s="6" t="s">
-        <v>125</v>
+      <c r="K62" t="s">
+        <v>137</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.8">
       <c r="B63" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="65" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="5" customFormat="1" ht="12.8">
       <c r="A65" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -26311,7 +26332,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="6"/>
+      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
@@ -26559,103 +26580,103 @@
       <c r="IV65" s="1"/>
       <c r="IW65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+    <row r="66" ht="12.8">
+      <c r="H66" s="1">
         <v>17</v>
       </c>
-      <c r="I66" s="9" t="s">
-        <v>127</v>
+      <c r="I66" s="7" t="s">
+        <v>108</v>
       </c>
-      <c r="J66" s="8" t="s">
-        <v>128</v>
+      <c r="J66" s="6" t="s">
+        <v>109</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>129</v>
+      <c r="K66" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
       <c r="B67" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="A70" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
       <c r="D71" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="12.8">
       <c r="D72" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="1">
         <v>1</v>
       </c>
-      <c r="I72" s="8"/>
+      <c r="I72" s="6"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.8">
       <c r="D73" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
-      <c r="I73" s="8"/>
+      <c r="I73" s="6"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.8">
       <c r="D74" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="I74" s="8"/>
+      <c r="I74" s="6"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.8">
       <c r="D75" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
-      <c r="I75" s="8"/>
+      <c r="I75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.8">
       <c r="B76" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.8">
       <c r="A79" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="12.8">
       <c r="B80" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="12.8">
       <c r="B81" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="12.8">
       <c r="A84" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="3" customFormat="1" ht="12.8">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -26663,17 +26684,17 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1" t="n">
+      <c r="H85" s="1">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
-      <c r="K85" s="10" t="s">
-        <v>138</v>
+      <c r="K85" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
@@ -26922,12 +26943,12 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="12.8">
       <c r="B86" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="5" customFormat="1" ht="12.8">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -26938,7 +26959,7 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="6"/>
+      <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
@@ -27186,7 +27207,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" s="5" customFormat="1" ht="12.8">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -27197,7 +27218,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
-      <c r="K99" s="6"/>
+      <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
@@ -27445,7 +27466,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="3" customFormat="1" ht="12.8">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -27456,7 +27477,7 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
-      <c r="K117" s="6"/>
+      <c r="K117" s="1"/>
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
@@ -27704,7 +27725,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="3" customFormat="1" ht="12.8">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -27715,7 +27736,7 @@
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
-      <c r="K118" s="6"/>
+      <c r="K118" s="1"/>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -27963,7 +27984,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="3" customFormat="1" ht="12.8">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -27974,7 +27995,7 @@
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
-      <c r="K119" s="6"/>
+      <c r="K119" s="1"/>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
@@ -28222,7 +28243,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" s="3" customFormat="1" ht="12.8">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -28233,7 +28254,7 @@
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
-      <c r="K126" s="6"/>
+      <c r="K126" s="1"/>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
@@ -28481,7 +28502,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" s="3" customFormat="1" ht="12.8">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -28492,7 +28513,7 @@
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
-      <c r="K127" s="6"/>
+      <c r="K127" s="1"/>
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
@@ -28740,7 +28761,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" s="3" customFormat="1" ht="12.8">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -28751,7 +28772,7 @@
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
-      <c r="K128" s="6"/>
+      <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
@@ -28999,7 +29020,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="3" customFormat="1" ht="12.8">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -29010,7 +29031,7 @@
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
-      <c r="K129" s="6"/>
+      <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
@@ -29258,7 +29279,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="3" customFormat="1" ht="12.8">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -29269,7 +29290,7 @@
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
-      <c r="K130" s="6"/>
+      <c r="K130" s="1"/>
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
@@ -29517,7 +29538,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="3" customFormat="1" ht="12.8">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -29528,7 +29549,7 @@
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
-      <c r="K157" s="6"/>
+      <c r="K157" s="1"/>
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -29776,7 +29797,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" s="3" customFormat="1" ht="12.8">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -29787,7 +29808,7 @@
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
-      <c r="K160" s="6"/>
+      <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
@@ -30035,7 +30056,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="3" customFormat="1" ht="12.8">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -30046,7 +30067,7 @@
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
-      <c r="K161" s="6"/>
+      <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
@@ -30294,7 +30315,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="3" customFormat="1" ht="12.8">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -30305,7 +30326,7 @@
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
       <c r="J236" s="1"/>
-      <c r="K236" s="6"/>
+      <c r="K236" s="1"/>
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
@@ -30553,7 +30574,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="5" customFormat="1" ht="12.8">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -30564,7 +30585,7 @@
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
       <c r="J240" s="1"/>
-      <c r="K240" s="6"/>
+      <c r="K240" s="1"/>
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
@@ -30812,7 +30833,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="1" ht="12.8">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -30823,7 +30844,7 @@
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
       <c r="J272" s="1"/>
-      <c r="K272" s="6"/>
+      <c r="K272" s="1"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
@@ -31071,7 +31092,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="5" customFormat="1" ht="12.8">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -31082,7 +31103,7 @@
       <c r="H286" s="1"/>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
-      <c r="K286" s="6"/>
+      <c r="K286" s="1"/>
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
@@ -31330,7 +31351,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="1" ht="12.8">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -31341,7 +31362,7 @@
       <c r="H287" s="1"/>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
-      <c r="K287" s="6"/>
+      <c r="K287" s="1"/>
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
@@ -31589,7 +31610,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="5" customFormat="1" ht="12.8">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -31600,7 +31621,7 @@
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
       <c r="J300" s="1"/>
-      <c r="K300" s="6"/>
+      <c r="K300" s="1"/>
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
@@ -31848,7 +31869,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="3" customFormat="1" ht="12.8">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -31859,7 +31880,7 @@
       <c r="H306" s="1"/>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
-      <c r="K306" s="6"/>
+      <c r="K306" s="1"/>
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
@@ -32107,7 +32128,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="3" customFormat="1" ht="12.8">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -32118,7 +32139,7 @@
       <c r="H313" s="1"/>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
-      <c r="K313" s="6"/>
+      <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
@@ -32366,7 +32387,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="3" customFormat="1" ht="12.8">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -32377,7 +32398,7 @@
       <c r="H337" s="1"/>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
-      <c r="K337" s="6"/>
+      <c r="K337" s="1"/>
       <c r="L337" s="1"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
@@ -32625,7 +32646,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="3" customFormat="1" ht="12.8">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -32636,7 +32657,7 @@
       <c r="H348" s="1"/>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
-      <c r="K348" s="6"/>
+      <c r="K348" s="1"/>
       <c r="L348" s="1"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
@@ -32884,7 +32905,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="5" customFormat="1" ht="12.8">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -32895,7 +32916,7 @@
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
-      <c r="K354" s="6"/>
+      <c r="K354" s="1"/>
       <c r="L354" s="1"/>
       <c r="M354" s="1"/>
       <c r="N354" s="1"/>
@@ -33143,7 +33164,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="5" customFormat="1" ht="12.8">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -33154,7 +33175,7 @@
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
-      <c r="K355" s="6"/>
+      <c r="K355" s="1"/>
       <c r="L355" s="1"/>
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
@@ -33402,7 +33423,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="5" customFormat="1" ht="12.8">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -33413,7 +33434,7 @@
       <c r="H366" s="1"/>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
-      <c r="K366" s="6"/>
+      <c r="K366" s="1"/>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
@@ -33661,7 +33682,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="1" ht="12.8">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -33672,7 +33693,7 @@
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
       <c r="J411" s="1"/>
-      <c r="K411" s="6"/>
+      <c r="K411" s="1"/>
       <c r="L411" s="1"/>
       <c r="M411" s="1"/>
       <c r="N411" s="1"/>
@@ -33920,7 +33941,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" s="3" customFormat="1" ht="12.8">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -33931,7 +33952,7 @@
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
       <c r="J415" s="1"/>
-      <c r="K415" s="6"/>
+      <c r="K415" s="1"/>
       <c r="L415" s="1"/>
       <c r="M415" s="1"/>
       <c r="N415" s="1"/>
@@ -34179,7 +34200,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="5" customFormat="1" ht="12.8">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -34190,7 +34211,7 @@
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
       <c r="J416" s="1"/>
-      <c r="K416" s="6"/>
+      <c r="K416" s="1"/>
       <c r="L416" s="1"/>
       <c r="M416" s="1"/>
       <c r="N416" s="1"/>
@@ -34438,7 +34459,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="1" ht="12.8">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -34449,7 +34470,7 @@
       <c r="H429" s="1"/>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
-      <c r="K429" s="6"/>
+      <c r="K429" s="1"/>
       <c r="L429" s="1"/>
       <c r="M429" s="1"/>
       <c r="N429" s="1"/>
@@ -34697,7 +34718,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="1" ht="12.8">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -34708,7 +34729,7 @@
       <c r="H430" s="1"/>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
-      <c r="K430" s="6"/>
+      <c r="K430" s="1"/>
       <c r="L430" s="1"/>
       <c r="M430" s="1"/>
       <c r="N430" s="1"/>
@@ -34956,7 +34977,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" s="3" customFormat="1" ht="12.8">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -34967,7 +34988,7 @@
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
       <c r="J439" s="1"/>
-      <c r="K439" s="6"/>
+      <c r="K439" s="1"/>
       <c r="L439" s="1"/>
       <c r="M439" s="1"/>
       <c r="N439" s="1"/>
@@ -35217,21 +35238,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H11 H14 H72:H1048576 H36:H70 H24:H34">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H23 H12:H13">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H71">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
